--- a/artfynd/Stornäsholmen artfynd.xlsx
+++ b/artfynd/Stornäsholmen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124741453</v>
+        <v>127062583</v>
       </c>
       <c r="B2" t="n">
-        <v>91699</v>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stornäsholmen, Stornäsholmen, Ång</t>
+          <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>705788</v>
+        <v>705431</v>
       </c>
       <c r="R2" t="n">
-        <v>7098196</v>
+        <v>7098017</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,28 +768,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127062579</v>
+        <v>127062582</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>80468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>705690</v>
+        <v>705428</v>
       </c>
       <c r="R3" t="n">
-        <v>7098154</v>
+        <v>7098018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,26 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127062583</v>
+        <v>127062581</v>
       </c>
       <c r="B4" t="n">
-        <v>95218</v>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,38 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>705431</v>
+        <v>705493</v>
       </c>
       <c r="R4" t="n">
-        <v>7098017</v>
+        <v>7098108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,7 +1004,7 @@
         <v>127062561</v>
       </c>
       <c r="B5" t="n">
-        <v>105381</v>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124741466</v>
+        <v>124741383</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>705793</v>
+        <v>705755</v>
       </c>
       <c r="R6" t="n">
         <v>7098171</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127062574</v>
+        <v>124741466</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,17 +1246,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stornäsholmen, Ång</t>
+          <t>Stornäsholmen, Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705932</v>
+        <v>705793</v>
       </c>
       <c r="R7" t="n">
-        <v>7097991</v>
+        <v>7098171</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1280,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,46 +1306,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anna Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127062577</v>
+        <v>127062571</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705784</v>
+        <v>705914</v>
       </c>
       <c r="R8" t="n">
-        <v>7098194</v>
+        <v>7097951</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,12 +1426,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granlåga med rynkskinn.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga med rynkskinn.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1494,32 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127062581</v>
+        <v>127062574</v>
       </c>
       <c r="B9" t="n">
-        <v>58488</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705493</v>
+        <v>705932</v>
       </c>
       <c r="R9" t="n">
-        <v>7098108</v>
+        <v>7097991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,6 +1540,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1601,50 +1576,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127062569</v>
+        <v>127062577</v>
       </c>
       <c r="B10" t="n">
-        <v>5196</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705923</v>
+        <v>705784</v>
       </c>
       <c r="R10" t="n">
-        <v>7097933</v>
+        <v>7098194</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,12 +1680,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Klen barklös granlåga.</t>
+          <t>Granlåga med rynkskinn.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Klen barklös granlåga.</t>
+          <t>Picea abies # Granlåga med rynkskinn.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127062571</v>
+        <v>124741453</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1714,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stornäsholmen, Ång</t>
+          <t>Stornäsholmen, Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705914</v>
+        <v>705788</v>
       </c>
       <c r="R11" t="n">
-        <v>7097951</v>
+        <v>7098196</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,22 +1768,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,50 +1794,30 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anna Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127062578</v>
+        <v>124741575</v>
       </c>
       <c r="B12" t="n">
-        <v>91699</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1880,28 +1830,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stornäsholmen, Ång</t>
+          <t>Stornäset, Stornäset, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705784</v>
+        <v>705833</v>
       </c>
       <c r="R12" t="n">
-        <v>7098194</v>
+        <v>7098254</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,22 +1875,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,68 +1901,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga med ullticka.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga med ullticka.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anna Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127062572</v>
+        <v>127062578</v>
       </c>
       <c r="B13" t="n">
-        <v>91210</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2022,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705914</v>
+        <v>705784</v>
       </c>
       <c r="R13" t="n">
-        <v>7097951</v>
+        <v>7098194</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,12 +2021,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga med ullticka.</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga med ullticka.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2114,48 +2044,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124741383</v>
+        <v>127062562</v>
       </c>
       <c r="B14" t="n">
-        <v>91541</v>
+        <v>95962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>2387</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stornäsholmen, Stornäsholmen, Ång</t>
+          <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705755</v>
+        <v>705813</v>
       </c>
       <c r="R14" t="n">
-        <v>7098171</v>
+        <v>7097844</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2179,29 +2109,29 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2209,22 +2139,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127062582</v>
+        <v>127062572</v>
       </c>
       <c r="B15" t="n">
-        <v>80119</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705428</v>
+        <v>705914</v>
       </c>
       <c r="R15" t="n">
-        <v>7098018</v>
+        <v>7097951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,6 +2242,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2328,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124744131</v>
+        <v>127062579</v>
       </c>
       <c r="B16" t="n">
-        <v>103803</v>
+        <v>4775</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,37 +2289,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nabben, Nabben, Ång</t>
+          <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705930</v>
+        <v>705690</v>
       </c>
       <c r="R16" t="n">
-        <v>7097926</v>
+        <v>7098154</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,22 +2348,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,64 +2374,89 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124741575</v>
+        <v>127062569</v>
       </c>
       <c r="B17" t="n">
-        <v>91699</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stornäset, Stornäset, Ång</t>
+          <t>Stornäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705833</v>
+        <v>705923</v>
       </c>
       <c r="R17" t="n">
-        <v>7098254</v>
+        <v>7097933</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2500,22 +2480,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,26 +2506,46 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Klen barklös granlåga.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen barklös granlåga.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127062565</v>
+        <v>124744131</v>
       </c>
       <c r="B18" t="n">
-        <v>103803</v>
+        <v>104628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,24 +2571,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stornäsholmen, Ång</t>
+          <t>Nabben, Nabben, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705913</v>
+        <v>705930</v>
       </c>
       <c r="R18" t="n">
-        <v>7097912</v>
+        <v>7097926</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2612,22 +2607,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,15 +2637,127 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Anna Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna Johansson, Lina Albertsen, André Bakas Carlsten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127062565</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stornäsholmen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>705913</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7097912</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
